--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,6 +780,124 @@
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129142369</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58366</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sluttningen, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>301768</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6438773</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 vuxna och 2 mindre fåglar som tigger mat.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -779,6 +779,16 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129138709</v>
       </c>
       <c r="B2" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>129142369</v>
       </c>
       <c r="B3" t="n">
-        <v>58366</v>
+        <v>58368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,6 +909,137 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129311075</v>
+      </c>
+      <c r="B4" t="n">
+        <v>88068</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1008</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Igelkottsröksvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycoperdon echinatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vattendraget, Röra Strand, Tjörn, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>301769</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6439009</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ungt exemplar av fruktkropp</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129138709</v>
       </c>
       <c r="B2" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>129142369</v>
       </c>
       <c r="B3" t="n">
-        <v>58368</v>
+        <v>58370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>129311075</v>
       </c>
       <c r="B4" t="n">
-        <v>88068</v>
+        <v>88070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,6 +1040,125 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129357434</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106303</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Slutet lövträdsbestånd, Röra Strand, Tjörn, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>301906</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6439041</v>
+      </c>
+      <c r="S5" t="n">
+        <v>70</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stor fina lövtröd i slutet bestånd med inslag av alar</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>129311075</v>
       </c>
       <c r="B4" t="n">
-        <v>88070</v>
+        <v>88071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>129357434</v>
       </c>
       <c r="B5" t="n">
-        <v>106303</v>
+        <v>106329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -1045,7 +1045,7 @@
         <v>129357434</v>
       </c>
       <c r="B5" t="n">
-        <v>106329</v>
+        <v>106331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -1045,7 +1045,7 @@
         <v>129357434</v>
       </c>
       <c r="B5" t="n">
-        <v>106331</v>
+        <v>106332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>129311075</v>
       </c>
       <c r="B4" t="n">
-        <v>88071</v>
+        <v>88074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>129357434</v>
       </c>
       <c r="B5" t="n">
-        <v>106332</v>
+        <v>106336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>129311075</v>
       </c>
       <c r="B4" t="n">
-        <v>88074</v>
+        <v>88076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>129357434</v>
       </c>
       <c r="B5" t="n">
-        <v>106336</v>
+        <v>106338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>129311075</v>
       </c>
       <c r="B4" t="n">
-        <v>88076</v>
+        <v>88080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>129357434</v>
       </c>
       <c r="B5" t="n">
-        <v>106338</v>
+        <v>106342</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>129311075</v>
       </c>
       <c r="B4" t="n">
-        <v>88080</v>
+        <v>88081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>129357434</v>
       </c>
       <c r="B5" t="n">
-        <v>106342</v>
+        <v>106352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -1045,7 +1045,7 @@
         <v>129357434</v>
       </c>
       <c r="B5" t="n">
-        <v>106352</v>
+        <v>106355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129138709</v>
       </c>
       <c r="B2" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>129142369</v>
       </c>
       <c r="B3" t="n">
-        <v>58370</v>
+        <v>58373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>129311075</v>
       </c>
       <c r="B4" t="n">
-        <v>88081</v>
+        <v>88109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>129357434</v>
       </c>
       <c r="B5" t="n">
-        <v>106355</v>
+        <v>106384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>129311075</v>
       </c>
       <c r="B4" t="n">
-        <v>88109</v>
+        <v>88115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>129357434</v>
       </c>
       <c r="B5" t="n">
-        <v>106384</v>
+        <v>106396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,6 +1158,908 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129711432</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Huseberg, Huseberg, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>301782</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6439068</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hackhål av spillkråka i en tall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129711664</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58105</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Huseberg, Huseberg, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>301811</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6438988</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera individer omkringflygandes bland tallarna. Sång identifierad separat i appen Merlin.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129711642</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58105</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Huseberg, Huseberg, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>301749</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6438866</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flertalet individer i träden, tydlig sång.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129722641</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Huseberg, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>301759</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6438993</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129747625</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vattendraget, Röra Strand, Tjörn, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>301761</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6439068</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Nya ringhack på andra sidan av träd med vit sav idag. Aktiv tretåig hackspett i området</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129746892</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stora vägen backen huseberg, Röra Strand, Tjörn, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>301746</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6438976</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackad i flera olika skeden på tall, omfattande med en del nya spår</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129747407</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vattendraget, Röra Strand, Tjörn, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>301759</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6438987</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska spår avbarkade tall</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>129311075</v>
       </c>
       <c r="B4" t="n">
-        <v>88115</v>
+        <v>88116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>129357434</v>
       </c>
       <c r="B5" t="n">
-        <v>106396</v>
+        <v>106397</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>129711432</v>
       </c>
       <c r="B6" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>129711664</v>
       </c>
       <c r="B7" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>129711642</v>
       </c>
       <c r="B8" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>129722641</v>
       </c>
       <c r="B9" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>129747625</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>129746892</v>
       </c>
       <c r="B11" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>129747407</v>
       </c>
       <c r="B12" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -914,7 +914,7 @@
         <v>129311075</v>
       </c>
       <c r="B4" t="n">
-        <v>88116</v>
+        <v>88121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>129357434</v>
       </c>
       <c r="B5" t="n">
-        <v>106397</v>
+        <v>106402</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2061,6 +2061,137 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129894214</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57894</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Huseberg, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>301759</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6438993</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Två st flygandes bland träden, sång inspelad med Merlin Bird ID.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -1565,10 +1565,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129722641</v>
+        <v>129746892</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,16 +1576,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1599,24 +1599,19 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Huseberg, Boh</t>
+          <t>Stora vägen backen huseberg, Röra Strand, Tjörn, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>301759</v>
+        <v>301746</v>
       </c>
       <c r="R9" t="n">
-        <v>6438993</v>
+        <v>6438976</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1640,27 +1635,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Hackad i flera olika skeden på tall, omfattande med en del nya spår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1680,22 +1675,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linéa Björnsdotter</t>
+          <t>Kristian  Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linéa Björnsdotter</t>
+          <t>Kristian  Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129747625</v>
+        <v>129747407</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,16 +1698,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1721,6 +1716,11 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>301761</v>
+        <v>301759</v>
       </c>
       <c r="R10" t="n">
-        <v>6439068</v>
+        <v>6438987</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Nya ringhack på andra sidan av träd med vit sav idag. Aktiv tretåig hackspett i området</t>
+          <t>Färska spår avbarkade tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1814,10 +1814,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129746892</v>
+        <v>129894214</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>57894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,16 +1825,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1842,25 +1842,34 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stora vägen backen huseberg, Röra Strand, Tjörn, Boh</t>
+          <t>Huseberg, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>301746</v>
+        <v>301759</v>
       </c>
       <c r="R11" t="n">
-        <v>6438976</v>
+        <v>6438993</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1884,27 +1893,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Hackad i flera olika skeden på tall, omfattande med en del nya spår</t>
+          <t>Två st flygandes bland träden, sång inspelad med Merlin Bird ID.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1924,22 +1933,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian  Larsson</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian  Larsson</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129747407</v>
+        <v>129747625</v>
       </c>
       <c r="B12" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,16 +1956,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1965,11 +1974,6 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1981,13 +1985,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>301759</v>
+        <v>301761</v>
       </c>
       <c r="R12" t="n">
-        <v>6438987</v>
+        <v>6439068</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2016,7 +2020,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2026,12 +2030,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska spår avbarkade tall</t>
+          <t>Nya ringhack på andra sidan av träd med vit sav idag. Aktiv tretåig hackspett i området</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2063,10 +2067,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129894214</v>
+        <v>129722641</v>
       </c>
       <c r="B13" t="n">
-        <v>57894</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2074,16 +2078,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103020</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2091,19 +2095,15 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2142,27 +2142,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Två st flygandes bland träden, sång inspelad med Merlin Bird ID.</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -1568,7 +1568,7 @@
         <v>129746892</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>129747407</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>129894214</v>
       </c>
       <c r="B11" t="n">
-        <v>57894</v>
+        <v>57893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>129747625</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129722641</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -1164,7 +1164,7 @@
         <v>129711432</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>129711664</v>
       </c>
       <c r="B7" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>129711642</v>
       </c>
       <c r="B8" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -1164,7 +1164,7 @@
         <v>129711432</v>
       </c>
       <c r="B6" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>129711664</v>
       </c>
       <c r="B7" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>129711642</v>
       </c>
       <c r="B8" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>129746892</v>
       </c>
       <c r="B9" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>129747407</v>
       </c>
       <c r="B10" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>129894214</v>
       </c>
       <c r="B11" t="n">
-        <v>57893</v>
+        <v>57896</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>129747625</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129722641</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2192,6 +2192,220 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130092093</v>
+      </c>
+      <c r="B14" t="n">
+        <v>95934</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Röstorp, Röstorp, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>301822</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6438959</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Suzi B Jagre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Suzi B Jagre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130091776</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4816</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100856</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Klibbtickgnagare</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dorcatoma punctulata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Mulsant &amp; Rey, 1864</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Röstorp, Röstorp, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>301847</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6438803</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Suzi B Jagre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Suzi B Jagre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -1296,7 +1296,7 @@
         <v>129711664</v>
       </c>
       <c r="B7" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>129711642</v>
       </c>
       <c r="B8" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>129894214</v>
       </c>
       <c r="B11" t="n">
-        <v>57896</v>
+        <v>57897</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2527,142 +2527,6 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>130164909</v>
-      </c>
-      <c r="B17" t="n">
-        <v>97694</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>224361</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Huperzia europaea</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Huseberg, Boh</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>301759</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6438993</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Tjörn</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Stenkyrka</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Funna i fuktig bergssluttning, ljusare skogsparti</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Linéa Björnsdotter</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Linéa Björnsdotter</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -2197,7 +2197,7 @@
         <v>130092093</v>
       </c>
       <c r="B14" t="n">
-        <v>95950</v>
+        <v>95952</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>130156915</v>
       </c>
       <c r="B16" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -1817,7 +1817,7 @@
         <v>129894214</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>129747625</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129726142</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>130092093</v>
       </c>
       <c r="B14" t="n">
-        <v>95952</v>
+        <v>96039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>130156915</v>
       </c>
       <c r="B16" t="n">
-        <v>92294</v>
+        <v>92381</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -1817,7 +1817,7 @@
         <v>129894214</v>
       </c>
       <c r="B11" t="n">
-        <v>57983</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>129747625</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129726142</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -2411,7 +2411,7 @@
         <v>130156915</v>
       </c>
       <c r="B16" t="n">
-        <v>92381</v>
+        <v>92384</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -2411,7 +2411,7 @@
         <v>130156915</v>
       </c>
       <c r="B16" t="n">
-        <v>92384</v>
+        <v>92410</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>130464844</v>
       </c>
       <c r="B17" t="n">
-        <v>57839</v>
+        <v>57865</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -2411,7 +2411,7 @@
         <v>130156915</v>
       </c>
       <c r="B16" t="n">
-        <v>92410</v>
+        <v>92411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -2411,7 +2411,7 @@
         <v>130156915</v>
       </c>
       <c r="B16" t="n">
-        <v>92411</v>
+        <v>92412</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -2532,7 +2532,7 @@
         <v>130464844</v>
       </c>
       <c r="B17" t="n">
-        <v>57865</v>
+        <v>57867</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -2532,7 +2532,7 @@
         <v>130464844</v>
       </c>
       <c r="B17" t="n">
-        <v>57867</v>
+        <v>57875</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -2532,7 +2532,7 @@
         <v>130464844</v>
       </c>
       <c r="B17" t="n">
-        <v>57875</v>
+        <v>57876</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -2532,7 +2532,7 @@
         <v>130464844</v>
       </c>
       <c r="B17" t="n">
-        <v>57876</v>
+        <v>57877</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2529,54 +2529,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130464844</v>
+        <v>130164909</v>
       </c>
       <c r="B17" t="n">
-        <v>57891</v>
+        <v>97822</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100048</v>
+        <v>221944</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2584,17 +2576,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Huseberg, Röra Strand, Tjörn, Boh</t>
+          <t>Huseberg, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>301860</v>
+        <v>301759</v>
       </c>
       <c r="R17" t="n">
-        <v>6438985</v>
+        <v>6438993</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2618,22 +2610,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Funna i fuktig bergssluttning, ljusare skogsparti</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2642,6 +2639,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2662,6 +2660,142 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130464844</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57891</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Huseberg, Röra Strand, Tjörn, Boh</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>301860</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6438985</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2797,6 +2797,134 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131817990</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58549</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Huseberg södra skogen, Boh</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>301794</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6438755</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2925,6 +2925,142 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131863268</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58059</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skogsstigen, Röra Strand, Tjörn, Boh</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>301735</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6439072</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Inspelad med Merlin Bird ID samt observerad spelandes i träd runt och nära barrskog och våtmark. Spel och sång har varit återkommande flera dagar och flera fåglar finns i närområdet. Permanent revir som observerats i 2 år nu.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -2802,7 +2802,7 @@
         <v>131817990</v>
       </c>
       <c r="B19" t="n">
-        <v>58549</v>
+        <v>58551</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>131863268</v>
       </c>
       <c r="B20" t="n">
-        <v>58059</v>
+        <v>58061</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -2802,7 +2802,7 @@
         <v>131817990</v>
       </c>
       <c r="B19" t="n">
-        <v>58551</v>
+        <v>58554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>131863268</v>
       </c>
       <c r="B20" t="n">
-        <v>58061</v>
+        <v>58064</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -2802,7 +2802,7 @@
         <v>131817990</v>
       </c>
       <c r="B19" t="n">
-        <v>58554</v>
+        <v>58559</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>131863268</v>
       </c>
       <c r="B20" t="n">
-        <v>58064</v>
+        <v>58069</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -2802,7 +2802,7 @@
         <v>131817990</v>
       </c>
       <c r="B19" t="n">
-        <v>58559</v>
+        <v>58561</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>131863268</v>
       </c>
       <c r="B20" t="n">
-        <v>58069</v>
+        <v>58071</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -2802,7 +2802,7 @@
         <v>131817990</v>
       </c>
       <c r="B19" t="n">
-        <v>58595</v>
+        <v>58597</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>131863268</v>
       </c>
       <c r="B20" t="n">
-        <v>58105</v>
+        <v>58107</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129138709</v>
+        <v>129311075</v>
       </c>
       <c r="B2" t="n">
-        <v>58100</v>
+        <v>88424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,53 +686,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>1008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Igelkottsröksvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycoperdon echinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Vattendraget, Röra Strand, Tjörn, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>301809</v>
+        <v>301769</v>
       </c>
       <c r="R2" t="n">
-        <v>6439000</v>
+        <v>6439009</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,17 +754,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kungsfåglar nära vattendrag, mycket aktiva</t>
+          <t>Ungt exemplar av fruktkropp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +785,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -793,64 +806,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129142369</v>
+        <v>130156915</v>
       </c>
       <c r="B3" t="n">
-        <v>58373</v>
+        <v>92567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103042</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sluttningen, Boh</t>
+          <t>Huseberg, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>301768</v>
+        <v>301759</v>
       </c>
       <c r="R3" t="n">
-        <v>6438773</v>
+        <v>6438993</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,17 +880,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2 vuxna och 2 mindre fåglar som tigger mat.</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,78 +906,73 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian  Larsson</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian  Larsson</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129311075</v>
+        <v>132769171</v>
       </c>
       <c r="B4" t="n">
-        <v>88121</v>
+        <v>79992</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1008</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Igelkottsröksvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycoperdon echinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vattendraget, Röra Strand, Tjörn, Boh</t>
+          <t>Dykärr, Dykärr, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>301769</v>
+        <v>301866</v>
       </c>
       <c r="R4" t="n">
-        <v>6439009</v>
+        <v>6438982</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,27 +996,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ungt exemplar av fruktkropp</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,67 +1022,70 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian  Larsson</t>
+          <t>Suzi B Jagre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian  Larsson</t>
+          <t>Suzi B Jagre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129357434</v>
+        <v>130464844</v>
       </c>
       <c r="B5" t="n">
-        <v>106402</v>
+        <v>57966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1089,17 +1093,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Slutet lövträdsbestånd, Röra Strand, Tjörn, Boh</t>
+          <t>Huseberg, Röra Strand, Tjörn, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>301906</v>
+        <v>301860</v>
       </c>
       <c r="R5" t="n">
-        <v>6439041</v>
+        <v>6438985</v>
       </c>
       <c r="S5" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,17 +1127,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Stor fina lövtröd i slutet bestånd med inslag av alar</t>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,29 +1151,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian  Larsson</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian  Larsson</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129711432</v>
+        <v>133193454</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,16 +1185,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1189,15 +1202,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1207,14 +1229,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Huseberg, Huseberg, Boh</t>
+          <t>Huseberg södra skogen, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>301782</v>
+        <v>301784</v>
       </c>
       <c r="R6" t="n">
-        <v>6439068</v>
+        <v>6438860</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1241,27 +1263,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska hackhål av spillkråka i en tall</t>
+          <t>Två stycken mindre hackspettar som trummar i lämpligt habitat. Revirhävd/parbildning? En fågel observerad flygandes bland träden, ej fotograferad. Trummandet höll på i ca 30 minuter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,11 +1294,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1293,10 +1310,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129711664</v>
+        <v>129711432</v>
       </c>
       <c r="B7" t="n">
-        <v>58112</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,16 +1321,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1321,11 +1338,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>adult</t>
@@ -1333,7 +1346,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1347,13 +1360,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>301811</v>
+        <v>301782</v>
       </c>
       <c r="R7" t="n">
-        <v>6438988</v>
+        <v>6439068</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1377,27 +1390,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Flera individer omkringflygandes bland tallarna. Sång identifierad separat i appen Merlin.</t>
+          <t>Färska hackhål av spillkråka i en tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1429,10 +1442,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129711642</v>
+        <v>129723566</v>
       </c>
       <c r="B8" t="n">
-        <v>58112</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,16 +1453,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1457,19 +1470,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1479,17 +1485,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Huseberg, Huseberg, Boh</t>
+          <t>Huseberg södra skogen, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>301749</v>
+        <v>301784</v>
       </c>
       <c r="R8" t="n">
-        <v>6438866</v>
+        <v>6438860</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1518,7 +1524,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1528,12 +1534,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Flertalet individer i träden, tydlig sång.</t>
+          <t>Träd med många potentiella bohål. Färska hackade spår hittade på andra sidan vägen i "norra" skogen.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1568,11 +1574,11 @@
         <v>129746892</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1690,11 +1696,11 @@
         <v>129747407</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1814,27 +1820,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129894214</v>
+        <v>129950270</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1844,7 +1850,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1852,6 +1858,12 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -1859,17 +1871,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Huseberg, Boh</t>
+          <t>Branten vid vägen, Röra Strand, Tjörn, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>301759</v>
+        <v>301782</v>
       </c>
       <c r="R11" t="n">
-        <v>6438993</v>
+        <v>6438867</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1893,27 +1905,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Två st flygandes bland träden, sång inspelad med Merlin Bird ID.</t>
+          <t>En fågels sång inspelad och identifierad med Merlin Bird ID appen</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1933,39 +1935,39 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linéa Björnsdotter</t>
+          <t>Kristian  Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linéa Björnsdotter</t>
+          <t>Kristian  Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129747625</v>
+        <v>132768239</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1974,6 +1976,11 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1981,17 +1988,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vattendraget, Röra Strand, Tjörn, Boh</t>
+          <t>Dykärr, Dykärr, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>301761</v>
+        <v>301940</v>
       </c>
       <c r="R12" t="n">
-        <v>6439068</v>
+        <v>6439015</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2015,27 +2022,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Nya ringhack på andra sidan av träd med vit sav idag. Aktiv tretåig hackspett i området</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2046,48 +2048,43 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian  Larsson</t>
+          <t>Suzi B Jagre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian  Larsson</t>
+          <t>Suzi B Jagre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129726142</v>
+        <v>132776139</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2098,7 +2095,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2108,17 +2105,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Huseberg, Boh</t>
+          <t>Huseberg södra skogen, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>301759</v>
+        <v>301794</v>
       </c>
       <c r="R13" t="n">
-        <v>6438993</v>
+        <v>6438755</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2142,27 +2139,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringade spår av tretåig hackspett på 4 olika trädstammar i detta område.</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2194,10 +2186,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130092093</v>
+        <v>132777099</v>
       </c>
       <c r="B14" t="n">
-        <v>96039</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,34 +2197,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2779</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röstorp, Röstorp, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>301822</v>
+        <v>301724</v>
       </c>
       <c r="R14" t="n">
-        <v>6438959</v>
+        <v>6438733</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -2259,22 +2256,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2301,10 +2298,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130091776</v>
+        <v>133010341</v>
       </c>
       <c r="B15" t="n">
-        <v>4816</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,37 +2309,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100856</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Klibbtickgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dorcatoma punctulata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Mulsant &amp; Rey, 1864</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Röstorp, Röstorp, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>301847</v>
+        <v>301844</v>
       </c>
       <c r="R15" t="n">
-        <v>6438803</v>
+        <v>6438806</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2366,29 +2372,19 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2396,22 +2392,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Suzi B Jagre</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Suzi B Jagre</t>
+          <t>Erland Svenson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130156915</v>
+        <v>130412256</v>
       </c>
       <c r="B16" t="n">
-        <v>92412</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,21 +2415,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6031</v>
+        <v>100067</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2441,21 +2437,32 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Huseberg, Boh</t>
+          <t>Huseberg södra skogen, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>301759</v>
+        <v>301784</v>
       </c>
       <c r="R16" t="n">
-        <v>6438993</v>
+        <v>6438860</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2482,22 +2489,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2508,11 +2515,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2529,46 +2531,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130164909</v>
+        <v>129722641</v>
       </c>
       <c r="B17" t="n">
-        <v>97822</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221944</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2610,36 +2608,35 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Funna i fuktig bergssluttning, ljusare skogsparti</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2663,10 +2660,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130464844</v>
+        <v>129747625</v>
       </c>
       <c r="B18" t="n">
-        <v>57891</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2674,16 +2671,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100048</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2691,26 +2688,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2718,17 +2696,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Huseberg, Röra Strand, Tjörn, Boh</t>
+          <t>Vattendraget, Röra Strand, Tjörn, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>301860</v>
+        <v>301761</v>
       </c>
       <c r="R18" t="n">
-        <v>6438985</v>
+        <v>6439068</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2752,22 +2730,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Nya ringhack på andra sidan av träd med vit sav idag. Aktiv tretåig hackspett i området</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2787,39 +2770,39 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linéa Björnsdotter</t>
+          <t>Kristian  Larsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linéa Björnsdotter</t>
+          <t>Kristian  Larsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131817990</v>
+        <v>129747759</v>
       </c>
       <c r="B19" t="n">
-        <v>58597</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103042</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2827,36 +2810,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Huseberg södra skogen, Boh</t>
+          <t>Vattendraget, Röra Strand, Tjörn, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>301794</v>
+        <v>301509</v>
       </c>
       <c r="R19" t="n">
-        <v>6438755</v>
+        <v>6439076</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2880,22 +2852,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Möjlig bohåla?</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2906,93 +2883,64 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linéa Björnsdotter</t>
+          <t>Kristian  Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linéa Björnsdotter</t>
+          <t>Kristian  Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131863268</v>
+        <v>130091776</v>
       </c>
       <c r="B20" t="n">
-        <v>58107</v>
+        <v>4818</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103020</v>
+        <v>100856</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Klibbtickgnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dorcatoma punctulata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Mulsant &amp; Rey, 1864</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skogsstigen, Röra Strand, Tjörn, Boh</t>
+          <t>Röstorp, Röstorp, Boh</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>301735</v>
+        <v>301847</v>
       </c>
       <c r="R20" t="n">
-        <v>6439072</v>
+        <v>6438803</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3016,34 +2964,29 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Inspelad med Merlin Bird ID samt observerad spelandes i träd runt och nära barrskog och våtmark. Spel och sång har varit återkommande flera dagar och flera fåglar finns i närområdet. Permanent revir som observerats i 2 år nu.</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -3051,65 +2994,76 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian  Larsson</t>
+          <t>Suzi B Jagre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian  Larsson</t>
+          <t>Suzi B Jagre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132777099</v>
+        <v>133008676</v>
       </c>
       <c r="B21" t="n">
-        <v>57955</v>
+        <v>57969</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Röstorp, Röstorp, Boh</t>
+          <t>Huseberg, Boh</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>301724</v>
+        <v>301759</v>
       </c>
       <c r="R21" t="n">
-        <v>6438733</v>
+        <v>6438993</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3133,22 +3087,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2 st gröngölingar som sjunger i Husebergskogen, inspelat med Merlin ID</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3159,43 +3118,48 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Suzi B Jagre</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Suzi B Jagre</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132776139</v>
+        <v>129138709</v>
       </c>
       <c r="B22" t="n">
-        <v>57955</v>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3203,30 +3167,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Huseberg södra skogen, Boh</t>
+          <t>Vattendraget, Röra Strand, Tjörn, Boh</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>301794</v>
+        <v>301809</v>
       </c>
       <c r="R22" t="n">
-        <v>6438755</v>
+        <v>6439000</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3250,22 +3220,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2022-06-01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Kungsfåglar nära vattendrag, mycket aktiva</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3276,73 +3241,83 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linéa Björnsdotter</t>
+          <t>Kristian  Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linéa Björnsdotter</t>
+          <t>Kristian  Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132769171</v>
+        <v>129711642</v>
       </c>
       <c r="B23" t="n">
-        <v>79952</v>
+        <v>58327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dykärr, Dykärr, Boh</t>
+          <t>Huseberg, Huseberg, Boh</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>301866</v>
+        <v>301749</v>
       </c>
       <c r="R23" t="n">
-        <v>6438982</v>
+        <v>6438866</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3366,22 +3341,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Flertalet individer i träden, tydlig sång.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3392,43 +3372,48 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Suzi B Jagre</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Suzi B Jagre</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132768239</v>
+        <v>129711664</v>
       </c>
       <c r="B24" t="n">
-        <v>57955</v>
+        <v>58327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3436,10 +3421,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3449,17 +3443,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dykärr, Dykärr, Boh</t>
+          <t>Huseberg, Huseberg, Boh</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>301940</v>
+        <v>301811</v>
       </c>
       <c r="R24" t="n">
-        <v>6439015</v>
+        <v>6438988</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3483,22 +3477,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Flera individer omkringflygandes bland tallarna. Sång identifierad separat i appen Merlin.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3509,74 +3508,83 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Suzi B Jagre</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Suzi B Jagre</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132856990</v>
+        <v>129894214</v>
       </c>
       <c r="B25" t="n">
-        <v>97991</v>
+        <v>58112</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221944</v>
+        <v>103020</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Huseberg södra skogen, Boh</t>
+          <t>Huseberg, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>301794</v>
+        <v>301759</v>
       </c>
       <c r="R25" t="n">
-        <v>6438755</v>
+        <v>6438993</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3600,22 +3608,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Två st flygandes bland träden, sång inspelad med Merlin Bird ID.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3647,10 +3660,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133010341</v>
+        <v>129950467</v>
       </c>
       <c r="B26" t="n">
-        <v>57955</v>
+        <v>58112</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3658,16 +3671,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3677,27 +3690,42 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Röstorp, Röstorp, Boh</t>
+          <t>Huseberg, Röra Strand, Tjörn, Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>301844</v>
+        <v>301706</v>
       </c>
       <c r="R26" t="n">
-        <v>6438806</v>
+        <v>6439130</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3721,12 +3749,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst två fåglar som spelats in och identifierats med Merlin Bird ID appen. Blåmes hörs även i inspelningen och även lite promenad ljud, ursäkta för det. Fåglarna har hörts i flera år och verkar ha permanent revir i skogen vid Huseberg.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3741,53 +3774,61 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Kristian  Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Svenson</t>
+          <t>Kristian  Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133008676</v>
+        <v>131863268</v>
       </c>
       <c r="B27" t="n">
-        <v>57952</v>
+        <v>58134</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102977</v>
+        <v>103020</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -3800,17 +3841,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Huseberg, Boh</t>
+          <t>Skogsstigen, Röra Strand, Tjörn, Boh</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>301759</v>
+        <v>301735</v>
       </c>
       <c r="R27" t="n">
-        <v>6438993</v>
+        <v>6439072</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3834,27 +3875,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2 st gröngölingar som sjunger i Husebergskogen, inspelat med Merlin ID</t>
+          <t>Inspelad med Merlin Bird ID samt observerad spelandes i träd runt och nära barrskog och våtmark. Spel och sång har varit återkommande flera dagar och flera fåglar finns i närområdet. Permanent revir som observerats i 2 år nu.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3865,24 +3906,1148 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131863462</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skog nära våtmark, Röra Strand, Tjörn, Boh</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>301672</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6439053</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>En vuxen hane spelandes i barrskog nära blandskogen och våtmarken i Huseberg. 2a året sång observeras och familjegruppen har övervintrat. Permanent revir antas</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129142369</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sluttningen, Boh</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>301768</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6438773</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>2 vuxna och 2 mindre fåglar som tigger mat.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131817990</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58624</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Huseberg södra skogen, Boh</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>301794</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6438755</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
           <t>Linéa Björnsdotter</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
+      <c r="AX30" t="inlineStr">
         <is>
           <t>Linéa Björnsdotter</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129135809</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Branten vid vägen, Röra Strand, Tjörn, Boh</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>301771</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6438904</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Fin hona upptäckt nära vägen i blötare terräng/dike</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129135857</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stora vägen backen huseberg, Röra Strand, Tjörn, Boh</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>301713</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6438929</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Överkörd padda på vägen i stora backen</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian  Larsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132130332</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stora våtmarken, Röra Strand, Tjörn, Boh</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>301658</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6439088</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Mellan 50-100 st vanlig groda som leker i en våtmark i Husebergskogen den 31 mars 2026</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Våtmark</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130091985</v>
+      </c>
+      <c r="B34" t="n">
+        <v>111175</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Dykärr, Dykärr, Boh</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>301915</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6438831</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Suzi B Jagre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Suzi B Jagre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130164909</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Huseberg, Boh</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>301759</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6438993</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Funna i fuktig bergssluttning, ljusare skogsparti</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132856990</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98054</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Huseberg södra skogen, Boh</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>301794</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6438755</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4587,10 +4587,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129135809</v>
+        <v>135817410</v>
       </c>
       <c r="B32" t="n">
-        <v>58826</v>
+        <v>56847</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4598,28 +4598,24 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>208242</v>
+        <v>205992</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
@@ -4632,20 +4628,24 @@
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Branten vid vägen, Röra Strand, Tjörn, Boh</t>
+          <t>Stora våtmarken, Röra Strand, Tjörn, Boh</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>301771</v>
+        <v>301658</v>
       </c>
       <c r="R32" t="n">
-        <v>6438904</v>
+        <v>6439088</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4669,17 +4669,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Fin hona upptäckt nära vägen i blötare terräng/dike</t>
+          <t>Inspelad i fält med pipistrelle box.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4688,63 +4698,54 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian  Larsson</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian  Larsson</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129135809</t>
+          <t>https://artportalen.se/Sighting/135817410</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129135857</v>
+        <v>135817781</v>
       </c>
       <c r="B33" t="n">
-        <v>58790</v>
+        <v>56838</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>208245</v>
+        <v>205998</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
@@ -4754,23 +4755,27 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stora vägen backen huseberg, Röra Strand, Tjörn, Boh</t>
+          <t>Stora våtmarken, Röra Strand, Tjörn, Boh</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>301713</v>
+        <v>301658</v>
       </c>
       <c r="R33" t="n">
-        <v>6438929</v>
+        <v>6439088</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4794,17 +4799,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>04:30</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Överkörd padda på vägen i stora backen</t>
+          <t>Inspelad i fält med pipistrelle ultraljudsbox.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4813,73 +4828,75 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian  Larsson</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian  Larsson</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129135857</t>
+          <t>https://artportalen.se/Sighting/135817781</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132130332</v>
+        <v>135819402</v>
       </c>
       <c r="B34" t="n">
-        <v>58839</v>
+        <v>56711</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>208249</v>
+        <v>206046</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
+          <t>fjolårsunge</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>parning/parningsceremonier</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4889,14 +4906,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stora våtmarken, Röra Strand, Tjörn, Boh</t>
+          <t>Huseberg södra skogen, Boh</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>301658</v>
+        <v>301794</v>
       </c>
       <c r="R34" t="n">
-        <v>6439088</v>
+        <v>6438755</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4923,27 +4940,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Mellan 50-100 st vanlig groda som leker i en våtmark i Husebergskogen den 31 mars 2026</t>
+          <t>2st födosökande älgar, en fjolårskalv och ko i bakgrunden (som inte syns på bilderna).</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4952,13 +4969,12 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Våtmark</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4975,16 +4991,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132130332</t>
+          <t>https://artportalen.se/Sighting/135819402</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130091985</v>
+        <v>129135809</v>
       </c>
       <c r="B35" t="n">
-        <v>111175</v>
+        <v>58826</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4992,37 +5008,54 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219677</v>
+        <v>208242</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dykärr, Dykärr, Boh</t>
+          <t>Branten vid vägen, Röra Strand, Tjörn, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>301915</v>
+        <v>301771</v>
       </c>
       <c r="R35" t="n">
-        <v>6438831</v>
+        <v>6438904</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5046,22 +5079,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fin hona upptäckt nära vägen i blötare terräng/dike</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5070,38 +5098,34 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Suzi B Jagre</t>
+          <t>Kristian  Larsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Suzi B Jagre</t>
+          <t>Kristian  Larsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130091985</t>
+          <t>https://artportalen.se/Sighting/129135809</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130164909</v>
+        <v>129135857</v>
       </c>
       <c r="B36" t="n">
-        <v>97977</v>
+        <v>58790</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5109,53 +5133,54 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221944</v>
+        <v>208245</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Huseberg, Boh</t>
+          <t>Stora vägen backen huseberg, Röra Strand, Tjörn, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>301759</v>
+        <v>301713</v>
       </c>
       <c r="R36" t="n">
-        <v>6438993</v>
+        <v>6438929</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5179,27 +5204,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Funna i fuktig bergssluttning, ljusare skogsparti</t>
+          <t>Överkörd padda på vägen i stora backen</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5212,35 +5227,30 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linéa Björnsdotter</t>
+          <t>Kristian  Larsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linéa Björnsdotter</t>
+          <t>Kristian  Larsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130164909</t>
+          <t>https://artportalen.se/Sighting/129135857</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132856990</v>
+        <v>132130332</v>
       </c>
       <c r="B37" t="n">
-        <v>98054</v>
+        <v>58839</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5248,27 +5258,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221944</v>
+        <v>208249</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5278,14 +5299,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Huseberg södra skogen, Boh</t>
+          <t>Stora våtmarken, Röra Strand, Tjörn, Boh</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>301794</v>
+        <v>301658</v>
       </c>
       <c r="R37" t="n">
-        <v>6438755</v>
+        <v>6439088</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5312,22 +5333,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Mellan 50-100 st vanlig groda som leker i en våtmark i Husebergskogen den 31 mars 2026</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5336,12 +5362,13 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Våtmark</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5357,6 +5384,389 @@
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132130332</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130091985</v>
+      </c>
+      <c r="B38" t="n">
+        <v>111175</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Dykärr, Dykärr, Boh</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>301915</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6438831</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Suzi B Jagre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Suzi B Jagre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130091985</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130164909</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Huseberg, Boh</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>301759</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6438993</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Funna i fuktig bergssluttning, ljusare skogsparti</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130164909</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132856990</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98054</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Huseberg södra skogen, Boh</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>301794</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6438755</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132856990</t>
         </is>
@@ -5400,6 +5810,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -4590,7 +4590,7 @@
         <v>135817410</v>
       </c>
       <c r="B32" t="n">
-        <v>56847</v>
+        <v>56849</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>135817781</v>
       </c>
       <c r="B33" t="n">
-        <v>56838</v>
+        <v>56840</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>135819402</v>
       </c>
       <c r="B34" t="n">
-        <v>56711</v>
+        <v>56713</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -4590,7 +4590,7 @@
         <v>135817410</v>
       </c>
       <c r="B32" t="n">
-        <v>56849</v>
+        <v>56850</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>135817781</v>
       </c>
       <c r="B33" t="n">
-        <v>56840</v>
+        <v>56841</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>135819402</v>
       </c>
       <c r="B34" t="n">
-        <v>56713</v>
+        <v>56714</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -4590,7 +4590,7 @@
         <v>135817410</v>
       </c>
       <c r="B32" t="n">
-        <v>56850</v>
+        <v>56854</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>135817781</v>
       </c>
       <c r="B33" t="n">
-        <v>56841</v>
+        <v>56845</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>135819402</v>
       </c>
       <c r="B34" t="n">
-        <v>56714</v>
+        <v>56718</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -4590,7 +4590,7 @@
         <v>135817410</v>
       </c>
       <c r="B32" t="n">
-        <v>56854</v>
+        <v>56855</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>135817781</v>
       </c>
       <c r="B33" t="n">
-        <v>56845</v>
+        <v>56846</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>135819402</v>
       </c>
       <c r="B34" t="n">
-        <v>56718</v>
+        <v>56719</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -4590,7 +4590,7 @@
         <v>135817410</v>
       </c>
       <c r="B32" t="n">
-        <v>56855</v>
+        <v>56860</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>135817781</v>
       </c>
       <c r="B33" t="n">
-        <v>56846</v>
+        <v>56851</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>135819402</v>
       </c>
       <c r="B34" t="n">
-        <v>56719</v>
+        <v>56724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 22581-2025 artfynd.xlsx
+++ b/artfynd/A 22581-2025 artfynd.xlsx
@@ -4590,7 +4590,7 @@
         <v>135817410</v>
       </c>
       <c r="B32" t="n">
-        <v>56860</v>
+        <v>56873</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>135817781</v>
       </c>
       <c r="B33" t="n">
-        <v>56851</v>
+        <v>56864</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>135819402</v>
       </c>
       <c r="B34" t="n">
-        <v>56724</v>
+        <v>56737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
